--- a/1_network_estimation/1_data_cleaning/Data_clean/MCAS/Estados_US/Edos_USA_2022/HAWAII_2022.xlsx
+++ b/1_network_estimation/1_data_cleaning/Data_clean/MCAS/Estados_US/Edos_USA_2022/HAWAII_2022.xlsx
@@ -351,28 +351,28 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D160"/>
+  <dimension ref="A1:D154"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Estado de Origen</t>
+          <t>mx_state</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Municipio Origen</t>
+          <t>mx_municipality</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Número de Matrículas</t>
+          <t>n_matriculas</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Porcentaje de Matrículas</t>
+          <t>pct_matriculas</t>
         </is>
       </c>
     </row>
@@ -395,6 +395,11 @@
       </c>
     </row>
     <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Aguascalientes</t>
+        </is>
+      </c>
       <c r="B3" t="inlineStr">
         <is>
           <t>Calvillo</t>
@@ -408,6 +413,11 @@
       </c>
     </row>
     <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Aguascalientes</t>
+        </is>
+      </c>
       <c r="B4" t="inlineStr">
         <is>
           <t>Total</t>
@@ -439,6 +449,11 @@
       </c>
     </row>
     <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Baja California</t>
+        </is>
+      </c>
       <c r="B6" t="inlineStr">
         <is>
           <t>Tijuana</t>
@@ -452,6 +467,11 @@
       </c>
     </row>
     <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Baja California</t>
+        </is>
+      </c>
       <c r="B7" t="inlineStr">
         <is>
           <t>Total</t>
@@ -483,6 +503,11 @@
       </c>
     </row>
     <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Baja California Sur</t>
+        </is>
+      </c>
       <c r="B9" t="inlineStr">
         <is>
           <t>Total</t>
@@ -514,6 +539,11 @@
       </c>
     </row>
     <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B11" t="inlineStr">
         <is>
           <t>Chenalhó</t>
@@ -527,6 +557,11 @@
       </c>
     </row>
     <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B12" t="inlineStr">
         <is>
           <t>Chicomuselo</t>
@@ -540,6 +575,11 @@
       </c>
     </row>
     <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B13" t="inlineStr">
         <is>
           <t>Mapastepec</t>
@@ -553,6 +593,11 @@
       </c>
     </row>
     <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B14" t="inlineStr">
         <is>
           <t>Motozintla</t>
@@ -566,9 +611,14 @@
       </c>
     </row>
     <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Ocozocoautla de Espinosa</t>
+          <t>Ocozocoautla De Espinosa</t>
         </is>
       </c>
       <c r="C15">
@@ -579,6 +629,11 @@
       </c>
     </row>
     <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B16" t="inlineStr">
         <is>
           <t>Total</t>
@@ -599,7 +654,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>San Juan de Sabinas</t>
+          <t>San Juan De Sabinas</t>
         </is>
       </c>
       <c r="C17">
@@ -610,6 +665,11 @@
       </c>
     </row>
     <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Coahuila</t>
+        </is>
+      </c>
       <c r="B18" t="inlineStr">
         <is>
           <t>Total</t>
@@ -630,7 +690,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Villa de Álvarez</t>
+          <t>Villa De Álvarez</t>
         </is>
       </c>
       <c r="C19">
@@ -641,6 +701,11 @@
       </c>
     </row>
     <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Colima</t>
+        </is>
+      </c>
       <c r="B20" t="inlineStr">
         <is>
           <t>Total</t>
@@ -656,7 +721,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Ciudad de México</t>
+          <t>Ciudad De México</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -672,6 +737,11 @@
       </c>
     </row>
     <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B22" t="inlineStr">
         <is>
           <t>Azcapotzalco</t>
@@ -685,6 +755,11 @@
       </c>
     </row>
     <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B23" t="inlineStr">
         <is>
           <t>Benito Juárez</t>
@@ -698,6 +773,11 @@
       </c>
     </row>
     <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B24" t="inlineStr">
         <is>
           <t>Coyoacán</t>
@@ -711,6 +791,11 @@
       </c>
     </row>
     <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B25" t="inlineStr">
         <is>
           <t>Cuauhtémoc</t>
@@ -724,6 +809,11 @@
       </c>
     </row>
     <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B26" t="inlineStr">
         <is>
           <t>Iztapalapa</t>
@@ -737,6 +827,11 @@
       </c>
     </row>
     <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B27" t="inlineStr">
         <is>
           <t>Miguel Hidalgo</t>
@@ -750,6 +845,11 @@
       </c>
     </row>
     <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B28" t="inlineStr">
         <is>
           <t>Venustiano Carranza</t>
@@ -763,6 +863,11 @@
       </c>
     </row>
     <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B29" t="inlineStr">
         <is>
           <t>Xochimilco</t>
@@ -776,6 +881,11 @@
       </c>
     </row>
     <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B30" t="inlineStr">
         <is>
           <t>Total</t>
@@ -807,6 +917,11 @@
       </c>
     </row>
     <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B32" t="inlineStr">
         <is>
           <t>Durango</t>
@@ -820,6 +935,11 @@
       </c>
     </row>
     <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B33" t="inlineStr">
         <is>
           <t>Guadalupe Victoria</t>
@@ -833,6 +953,11 @@
       </c>
     </row>
     <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B34" t="inlineStr">
         <is>
           <t>Total</t>
@@ -848,7 +973,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Estado de México</t>
+          <t>Estado De México</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -864,9 +989,14 @@
       </c>
     </row>
     <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Ecatepec de Morelos</t>
+          <t>Ecatepec De Morelos</t>
         </is>
       </c>
       <c r="C36">
@@ -877,9 +1007,14 @@
       </c>
     </row>
     <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Ixtapan de la Sal</t>
+          <t>Ixtapan De La Sal</t>
         </is>
       </c>
       <c r="C37">
@@ -890,6 +1025,11 @@
       </c>
     </row>
     <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B38" t="inlineStr">
         <is>
           <t>Malinalco</t>
@@ -903,6 +1043,11 @@
       </c>
     </row>
     <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B39" t="inlineStr">
         <is>
           <t>Nezahualcóyotl</t>
@@ -916,6 +1061,11 @@
       </c>
     </row>
     <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B40" t="inlineStr">
         <is>
           <t>Ozumba</t>
@@ -929,9 +1079,14 @@
       </c>
     </row>
     <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>San Felipe del Progreso</t>
+          <t>San Felipe Del Progreso</t>
         </is>
       </c>
       <c r="C41">
@@ -942,6 +1097,11 @@
       </c>
     </row>
     <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B42" t="inlineStr">
         <is>
           <t>Sultepec</t>
@@ -955,6 +1115,11 @@
       </c>
     </row>
     <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B43" t="inlineStr">
         <is>
           <t>Temascalcingo</t>
@@ -968,6 +1133,11 @@
       </c>
     </row>
     <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B44" t="inlineStr">
         <is>
           <t>Texcoco</t>
@@ -981,9 +1151,14 @@
       </c>
     </row>
     <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Tlalnepantla de Baz</t>
+          <t>Tlalnepantla De Baz</t>
         </is>
       </c>
       <c r="C45">
@@ -994,6 +1169,11 @@
       </c>
     </row>
     <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B46" t="inlineStr">
         <is>
           <t>Toluca</t>
@@ -1007,6 +1187,11 @@
       </c>
     </row>
     <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B47" t="inlineStr">
         <is>
           <t>Tultepec</t>
@@ -1020,6 +1205,11 @@
       </c>
     </row>
     <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B48" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1051,6 +1241,11 @@
       </c>
     </row>
     <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B50" t="inlineStr">
         <is>
           <t>Huanímaro</t>
@@ -1064,6 +1259,11 @@
       </c>
     </row>
     <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B51" t="inlineStr">
         <is>
           <t>León</t>
@@ -1077,6 +1277,11 @@
       </c>
     </row>
     <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B52" t="inlineStr">
         <is>
           <t>Moroleón</t>
@@ -1090,6 +1295,11 @@
       </c>
     </row>
     <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B53" t="inlineStr">
         <is>
           <t>Salamanca</t>
@@ -1103,6 +1313,11 @@
       </c>
     </row>
     <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B54" t="inlineStr">
         <is>
           <t>Tarimoro</t>
@@ -1116,6 +1331,11 @@
       </c>
     </row>
     <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B55" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1136,7 +1356,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Acapulco de Juárez</t>
+          <t>Acapulco De Juárez</t>
         </is>
       </c>
       <c r="C56">
@@ -1147,9 +1367,14 @@
       </c>
     </row>
     <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Ayutla de los Libres</t>
+          <t>Ayutla De Los Libres</t>
         </is>
       </c>
       <c r="C57">
@@ -1160,9 +1385,14 @@
       </c>
     </row>
     <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Buenavista de Cuéllar</t>
+          <t>Buenavista De Cuéllar</t>
         </is>
       </c>
       <c r="C58">
@@ -1173,6 +1403,11 @@
       </c>
     </row>
     <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B59" t="inlineStr">
         <is>
           <t>Cuajinicuilapa</t>
@@ -1186,6 +1421,11 @@
       </c>
     </row>
     <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B60" t="inlineStr">
         <is>
           <t>Zirándaro</t>
@@ -1199,6 +1439,11 @@
       </c>
     </row>
     <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B61" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1230,6 +1475,11 @@
       </c>
     </row>
     <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B63" t="inlineStr">
         <is>
           <t>Ajacuba</t>
@@ -1243,6 +1493,11 @@
       </c>
     </row>
     <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B64" t="inlineStr">
         <is>
           <t>Chapantongo</t>
@@ -1256,6 +1511,11 @@
       </c>
     </row>
     <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B65" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1287,6 +1547,11 @@
       </c>
     </row>
     <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B67" t="inlineStr">
         <is>
           <t>Guadalajara</t>
@@ -1300,6 +1565,11 @@
       </c>
     </row>
     <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B68" t="inlineStr">
         <is>
           <t>Huejúcar</t>
@@ -1313,9 +1583,14 @@
       </c>
     </row>
     <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Jilotlán de los Dolores</t>
+          <t>Jilotlán De Los Dolores</t>
         </is>
       </c>
       <c r="C69">
@@ -1326,6 +1601,11 @@
       </c>
     </row>
     <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B70" t="inlineStr">
         <is>
           <t>La Huerta</t>
@@ -1339,9 +1619,14 @@
       </c>
     </row>
     <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>La Manzanilla de la Paz</t>
+          <t>La Manzanilla De La Paz</t>
         </is>
       </c>
       <c r="C71">
@@ -1352,6 +1637,11 @@
       </c>
     </row>
     <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B72" t="inlineStr">
         <is>
           <t>Magdalena</t>
@@ -1365,6 +1655,11 @@
       </c>
     </row>
     <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B73" t="inlineStr">
         <is>
           <t>San Martín Hidalgo</t>
@@ -1378,6 +1673,11 @@
       </c>
     </row>
     <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B74" t="inlineStr">
         <is>
           <t>Teocaltiche</t>
@@ -1391,9 +1691,14 @@
       </c>
     </row>
     <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Tizapán el Alto</t>
+          <t>Tizapán El Alto</t>
         </is>
       </c>
       <c r="C75">
@@ -1404,9 +1709,14 @@
       </c>
     </row>
     <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Unión de Tula</t>
+          <t>Unión De Tula</t>
         </is>
       </c>
       <c r="C76">
@@ -1417,6 +1727,11 @@
       </c>
     </row>
     <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B77" t="inlineStr">
         <is>
           <t>Villa Corona</t>
@@ -1430,6 +1745,11 @@
       </c>
     </row>
     <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B78" t="inlineStr">
         <is>
           <t>Zapopan</t>
@@ -1443,9 +1763,14 @@
       </c>
     </row>
     <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Zapotlán el Grande</t>
+          <t>Zapotlán El Grande</t>
         </is>
       </c>
       <c r="C79">
@@ -1456,6 +1781,11 @@
       </c>
     </row>
     <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B80" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1487,6 +1817,11 @@
       </c>
     </row>
     <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B82" t="inlineStr">
         <is>
           <t>Indaparapeo</t>
@@ -1500,6 +1835,11 @@
       </c>
     </row>
     <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B83" t="inlineStr">
         <is>
           <t>Jiquilpan</t>
@@ -1513,6 +1853,11 @@
       </c>
     </row>
     <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B84" t="inlineStr">
         <is>
           <t>La Piedad</t>
@@ -1526,6 +1871,11 @@
       </c>
     </row>
     <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B85" t="inlineStr">
         <is>
           <t>Puruándiro</t>
@@ -1539,6 +1889,11 @@
       </c>
     </row>
     <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B86" t="inlineStr">
         <is>
           <t>Sahuayo</t>
@@ -1552,6 +1907,11 @@
       </c>
     </row>
     <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B87" t="inlineStr">
         <is>
           <t>Tacámbaro</t>
@@ -1565,6 +1925,11 @@
       </c>
     </row>
     <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B88" t="inlineStr">
         <is>
           <t>Tangamandapio</t>
@@ -1578,6 +1943,11 @@
       </c>
     </row>
     <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B89" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1598,7 +1968,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Ixtlán del Río</t>
+          <t>Ixtlán Del Río</t>
         </is>
       </c>
       <c r="C90">
@@ -1609,6 +1979,11 @@
       </c>
     </row>
     <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Nayarit</t>
+        </is>
+      </c>
       <c r="B91" t="inlineStr">
         <is>
           <t>La Yesca</t>
@@ -1622,6 +1997,11 @@
       </c>
     </row>
     <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Nayarit</t>
+        </is>
+      </c>
       <c r="B92" t="inlineStr">
         <is>
           <t>Rosamorada</t>
@@ -1635,6 +2015,11 @@
       </c>
     </row>
     <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Nayarit</t>
+        </is>
+      </c>
       <c r="B93" t="inlineStr">
         <is>
           <t>San Blas</t>
@@ -1648,6 +2033,11 @@
       </c>
     </row>
     <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Nayarit</t>
+        </is>
+      </c>
       <c r="B94" t="inlineStr">
         <is>
           <t>Santiago Ixcuintla</t>
@@ -1661,6 +2051,11 @@
       </c>
     </row>
     <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Nayarit</t>
+        </is>
+      </c>
       <c r="B95" t="inlineStr">
         <is>
           <t>Tepic</t>
@@ -1674,6 +2069,11 @@
       </c>
     </row>
     <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Nayarit</t>
+        </is>
+      </c>
       <c r="B96" t="inlineStr">
         <is>
           <t>Tuxpan</t>
@@ -1687,6 +2087,11 @@
       </c>
     </row>
     <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Nayarit</t>
+        </is>
+      </c>
       <c r="B97" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1707,7 +2112,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Chalcatongo de Hidalgo</t>
+          <t>Chalcatongo De Hidalgo</t>
         </is>
       </c>
       <c r="C98">
@@ -1718,6 +2123,11 @@
       </c>
     </row>
     <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B99" t="inlineStr">
         <is>
           <t>Cosolapa</t>
@@ -1731,9 +2141,14 @@
       </c>
     </row>
     <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Heroica Ciudad de Tlaxiaco</t>
+          <t>Heroica Ciudad De Tlaxiaco</t>
         </is>
       </c>
       <c r="C100">
@@ -1744,9 +2159,14 @@
       </c>
     </row>
     <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Ixtlán de Juárez</t>
+          <t>Ixtlán De Juárez</t>
         </is>
       </c>
       <c r="C101">
@@ -1757,9 +2177,14 @@
       </c>
     </row>
     <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Putla Villa de Guerrero</t>
+          <t>Putla Villa De Guerrero</t>
         </is>
       </c>
       <c r="C102">
@@ -1770,6 +2195,11 @@
       </c>
     </row>
     <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B103" t="inlineStr">
         <is>
           <t>San Esteban Atatlahuca</t>
@@ -1783,6 +2213,11 @@
       </c>
     </row>
     <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B104" t="inlineStr">
         <is>
           <t>San Juan Atepec</t>
@@ -1796,6 +2231,11 @@
       </c>
     </row>
     <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B105" t="inlineStr">
         <is>
           <t>San Juan Bautista Valle Nacional</t>
@@ -1809,6 +2249,11 @@
       </c>
     </row>
     <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B106" t="inlineStr">
         <is>
           <t>Santa Catarina Juquila</t>
@@ -1822,6 +2267,11 @@
       </c>
     </row>
     <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B107" t="inlineStr">
         <is>
           <t>Santa Cruz Zenzontepec</t>
@@ -1835,6 +2285,11 @@
       </c>
     </row>
     <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B108" t="inlineStr">
         <is>
           <t>Santa María Cortijo</t>
@@ -1848,6 +2303,11 @@
       </c>
     </row>
     <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B109" t="inlineStr">
         <is>
           <t>Santiago Choápam</t>
@@ -1861,6 +2321,11 @@
       </c>
     </row>
     <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B110" t="inlineStr">
         <is>
           <t>Santiago Comaltepec</t>
@@ -1874,6 +2339,11 @@
       </c>
     </row>
     <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B111" t="inlineStr">
         <is>
           <t>Santiago Pinotepa Nacional</t>
@@ -1887,6 +2357,11 @@
       </c>
     </row>
     <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B112" t="inlineStr">
         <is>
           <t>Santo Tomás Ocotepec</t>
@@ -1900,9 +2375,14 @@
       </c>
     </row>
     <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Villa de Tututepec de Melchor Ocampo</t>
+          <t>Villa De Tututepec De Melchor Ocampo</t>
         </is>
       </c>
       <c r="C113">
@@ -1913,6 +2393,11 @@
       </c>
     </row>
     <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B114" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1944,6 +2429,11 @@
       </c>
     </row>
     <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B116" t="inlineStr">
         <is>
           <t>Chinantla</t>
@@ -1957,9 +2447,14 @@
       </c>
     </row>
     <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Huehuetlán el Chico</t>
+          <t>Huehuetlán El Chico</t>
         </is>
       </c>
       <c r="C117">
@@ -1970,9 +2465,14 @@
       </c>
     </row>
     <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Los Reyes de Juárez</t>
+          <t>Los Reyes De Juárez</t>
         </is>
       </c>
       <c r="C118">
@@ -1983,6 +2483,11 @@
       </c>
     </row>
     <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B119" t="inlineStr">
         <is>
           <t>Puebla</t>
@@ -1996,6 +2501,11 @@
       </c>
     </row>
     <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B120" t="inlineStr">
         <is>
           <t>San Andrés Cholula</t>
@@ -2009,6 +2519,11 @@
       </c>
     </row>
     <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B121" t="inlineStr">
         <is>
           <t>San Pedro Cholula</t>
@@ -2022,6 +2537,11 @@
       </c>
     </row>
     <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B122" t="inlineStr">
         <is>
           <t>Soltepec</t>
@@ -2035,6 +2555,11 @@
       </c>
     </row>
     <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B123" t="inlineStr">
         <is>
           <t>Tehuacán</t>
@@ -2048,6 +2573,11 @@
       </c>
     </row>
     <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B124" t="inlineStr">
         <is>
           <t>Tepeaca</t>
@@ -2061,9 +2591,14 @@
       </c>
     </row>
     <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Tetela de Ocampo</t>
+          <t>Tetela De Ocampo</t>
         </is>
       </c>
       <c r="C125">
@@ -2074,6 +2609,11 @@
       </c>
     </row>
     <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B126" t="inlineStr">
         <is>
           <t>Tianguismanalco</t>
@@ -2087,6 +2627,11 @@
       </c>
     </row>
     <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B127" t="inlineStr">
         <is>
           <t>Tochimilco</t>
@@ -2100,6 +2645,11 @@
       </c>
     </row>
     <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B128" t="inlineStr">
         <is>
           <t>Total</t>
@@ -2131,6 +2681,11 @@
       </c>
     </row>
     <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>Querétaro</t>
+        </is>
+      </c>
       <c r="B130" t="inlineStr">
         <is>
           <t>Total</t>
@@ -2162,6 +2717,11 @@
       </c>
     </row>
     <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B132" t="inlineStr">
         <is>
           <t>Total</t>
@@ -2193,6 +2753,11 @@
       </c>
     </row>
     <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>Sonora</t>
+        </is>
+      </c>
       <c r="B134" t="inlineStr">
         <is>
           <t>Empalme</t>
@@ -2206,6 +2771,11 @@
       </c>
     </row>
     <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>Sonora</t>
+        </is>
+      </c>
       <c r="B135" t="inlineStr">
         <is>
           <t>Guaymas</t>
@@ -2219,6 +2789,11 @@
       </c>
     </row>
     <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>Sonora</t>
+        </is>
+      </c>
       <c r="B136" t="inlineStr">
         <is>
           <t>Naco</t>
@@ -2232,6 +2807,11 @@
       </c>
     </row>
     <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>Sonora</t>
+        </is>
+      </c>
       <c r="B137" t="inlineStr">
         <is>
           <t>Nogales</t>
@@ -2245,6 +2825,11 @@
       </c>
     </row>
     <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>Sonora</t>
+        </is>
+      </c>
       <c r="B138" t="inlineStr">
         <is>
           <t>Total</t>
@@ -2276,6 +2861,11 @@
       </c>
     </row>
     <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B140" t="inlineStr">
         <is>
           <t>Atlangatepec</t>
@@ -2289,6 +2879,11 @@
       </c>
     </row>
     <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B141" t="inlineStr">
         <is>
           <t>Huamantla</t>
@@ -2302,6 +2897,11 @@
       </c>
     </row>
     <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B142" t="inlineStr">
         <is>
           <t>Natívitas</t>
@@ -2315,6 +2915,11 @@
       </c>
     </row>
     <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B143" t="inlineStr">
         <is>
           <t>Panotla</t>
@@ -2328,6 +2933,11 @@
       </c>
     </row>
     <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B144" t="inlineStr">
         <is>
           <t>Terrenate</t>
@@ -2341,6 +2951,11 @@
       </c>
     </row>
     <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B145" t="inlineStr">
         <is>
           <t>Tlaxcala</t>
@@ -2354,6 +2969,11 @@
       </c>
     </row>
     <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B146" t="inlineStr">
         <is>
           <t>Total</t>
@@ -2385,9 +3005,14 @@
       </c>
     </row>
     <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Ignacio de la Llave</t>
+          <t>Ignacio De La Llave</t>
         </is>
       </c>
       <c r="C148">
@@ -2398,6 +3023,11 @@
       </c>
     </row>
     <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B149" t="inlineStr">
         <is>
           <t>Veracruz</t>
@@ -2411,6 +3041,11 @@
       </c>
     </row>
     <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B150" t="inlineStr">
         <is>
           <t>Total</t>
@@ -2442,6 +3077,11 @@
       </c>
     </row>
     <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B152" t="inlineStr">
         <is>
           <t>Jalpa</t>
@@ -2455,6 +3095,11 @@
       </c>
     </row>
     <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B153" t="inlineStr">
         <is>
           <t>Total</t>
@@ -2478,41 +3123,6 @@
       </c>
       <c r="D154">
         <v>1</v>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" t="inlineStr">
-        <is>
-          <t>Tamaño de la muestra: 566,547</t>
-        </is>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" t="inlineStr">
-        <is>
-          <t>Fuente: Expedición de Matrículas Consulares de Alta Seguridad en los Consulados de México en E.E.U.U.</t>
-        </is>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" t="inlineStr">
-        <is>
-          <t>Elaborado por: Análisis de Información, Instituto de los Mexicanos en el Exterior</t>
-        </is>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" t="inlineStr">
-        <is>
-          <t>Secretaría de Relaciones Exteriores</t>
-        </is>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" t="inlineStr">
-        <is>
-          <t>Mayo de 2023</t>
-        </is>
       </c>
     </row>
   </sheetData>
